--- a/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
+++ b/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE0870D-2ED8-BD4C-80D6-1C759EFC6494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D274D4-A97B-1E4C-A2AE-2A0E9EE14184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="24540" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -239,9 +239,6 @@
     <t>stem_suspension</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>rear_suspension</t>
   </si>
   <si>
@@ -405,13 +402,19 @@
   </si>
   <si>
     <t>Suggested Rider</t>
+  </si>
+  <si>
+    <t>cane creek invert</t>
+  </si>
+  <si>
+    <t>Measurements with Cane Creek Invert Suspension Fork. 40mm travel, 435mm Axle to Crown Fork @ 45mm Offset. Frame is compatible with 30-50mm Travels. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -425,6 +428,12 @@
     </font>
     <font>
       <sz val="17"/>
+      <color rgb="FF242729"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <color rgb="FF242729"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -450,10 +459,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,7 +779,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -803,6 +813,9 @@
       <c r="B7" t="s">
         <v>10</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -986,22 +999,22 @@
         <v>430</v>
       </c>
       <c r="I14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1056,25 +1069,25 @@
         <v>1111</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="N16" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1100,7 +1113,7 @@
         <v>830.58</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1126,7 +1139,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1152,7 +1165,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -1175,7 +1188,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -1197,28 +1210,31 @@
       <c r="H21">
         <v>435</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -1241,12 +1257,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -1269,7 +1285,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -1292,7 +1308,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -1315,7 +1331,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -1344,7 +1360,7 @@
         <v>187.96</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -1421,47 +1437,47 @@
     </row>
     <row r="35" spans="1:9" ht="23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" t="s">
         <v>100</v>
       </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
       <c r="C35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
         <v>102</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -1513,60 +1529,54 @@
       <c r="A44" t="s">
         <v>66</v>
       </c>
-      <c r="B44" t="s">
-        <v>59</v>
+      <c r="B44">
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>67</v>
       </c>
-      <c r="B45" t="s">
-        <v>68</v>
-      </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" t="s">
         <v>70</v>
-      </c>
-      <c r="B47" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" t="s">
         <v>72</v>
-      </c>
-      <c r="B48" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s">
         <v>59</v>
@@ -1574,120 +1584,120 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" t="s">
         <v>78</v>
-      </c>
-      <c r="B53" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" t="s">
         <v>84</v>
-      </c>
-      <c r="B58" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B69">
         <v>4795</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
+++ b/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D274D4-A97B-1E4C-A2AE-2A0E9EE14184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9056112-281C-8D4D-9734-CC774D6B7532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="24540" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -287,9 +287,6 @@
     <t>routing_shifter</t>
   </si>
   <si>
-    <t>external</t>
-  </si>
-  <si>
     <t>routing_dropper</t>
   </si>
   <si>
@@ -408,6 +405,9 @@
   </si>
   <si>
     <t>Measurements with Cane Creek Invert Suspension Fork. 40mm travel, 435mm Axle to Crown Fork @ 45mm Offset. Frame is compatible with 30-50mm Travels. </t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -779,7 +779,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -814,7 +814,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -999,22 +999,22 @@
         <v>430</v>
       </c>
       <c r="I14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1069,22 +1069,22 @@
         <v>1111</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1211,7 +1211,7 @@
         <v>435</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1437,47 +1437,47 @@
     </row>
     <row r="35" spans="1:9" ht="23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
         <v>99</v>
       </c>
-      <c r="B35" t="s">
-        <v>100</v>
-      </c>
       <c r="C35" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
         <v>101</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -1614,90 +1614,90 @@
       <c r="A58" t="s">
         <v>83</v>
       </c>
-      <c r="B58" t="s">
-        <v>84</v>
+      <c r="B58" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>85</v>
-      </c>
-      <c r="B59" t="s">
         <v>84</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B69">
         <v>4795</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
+++ b/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9056112-281C-8D4D-9734-CC774D6B7532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60696208-5388-CA40-9273-29B50821CE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="24540" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/52f98c74e4b097d8674dc15e/1724560233343-60NHN9R6M5SP7QZ27G73/2024-MADE-BIke-Show-Chumba-Cenote-Gravel-Bike-17.jpg?format=1500w</t>
   </si>
 </sst>
 </file>
@@ -806,6 +809,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+    </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>

--- a/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
+++ b/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60696208-5388-CA40-9273-29B50821CE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6068432-B981-BD4D-BF7E-A1452CD48E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="24540" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/52f98c74e4b097d8674dc15e/1724560233343-60NHN9R6M5SP7QZ27G73/2024-MADE-BIke-Show-Chumba-Cenote-Gravel-Bike-17.jpg?format=1500w</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri, USA</t>
   </si>
 </sst>
 </file>
@@ -763,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1708,6 +1714,14 @@
         <v>105</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
+++ b/data/gravel/Chumba Cenote Ti (short) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6068432-B981-BD4D-BF7E-A1452CD48E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2176F2-8747-6A4F-94EF-7B10C547FDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="24540" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="134">
   <si>
     <t>brand</t>
   </si>
@@ -417,6 +417,24 @@
   </si>
   <si>
     <t>Kansas City, Missouri, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -769,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1575,150 +1593,180 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>76</v>
-      </c>
-      <c r="B52" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>83</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>124</v>
+        <v>76</v>
+      </c>
+      <c r="B58" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>84</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>124</v>
+        <v>77</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>90</v>
+        <v>84</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69">
-        <v>4795</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>97</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75">
+        <v>4795</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>126</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>127</v>
       </c>
     </row>
